--- a/output/pdf_financials_xlsx/URZ.xlsx
+++ b/output/pdf_financials_xlsx/URZ.xlsx
@@ -5571,52 +5571,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.875772</v>
+        <v>2.137979</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>4.206199</v>
+        <v>1.997642</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.323621</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.08456</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.955109</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.524956</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.866472</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.188765</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.638278</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.61306</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.398405</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.117687</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.395546</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.86551</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.214185</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.801212</v>
       </c>
     </row>
     <row r="93">
@@ -6956,19 +6956,19 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.457463</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.350787</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.340009</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>2.632919</v>
+        <v>2.438721</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.349346</v>
+        <v>1.232489</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -9026,7 +9026,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10020,7 +10024,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -10718,7 +10726,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11716,7 +11728,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -12458,7 +12474,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13032,7 +13052,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>2.137979</v>
       </c>
@@ -21642,7 +21666,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/URZ.xlsx
+++ b/output/pdf_financials_xlsx/URZ.xlsx
@@ -1039,28 +1039,28 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001693</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00071</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.004844</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000103</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000137</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00044</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000484</v>
       </c>
     </row>
     <row r="13">
@@ -1934,28 +1934,28 @@
         <v>-2.955304</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.86642</v>
+        <v>-2.868113</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.333994</v>
+        <v>-4.334704</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.13542</v>
+        <v>-5.140264</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.347599</v>
+        <v>-3.347702</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.936559</v>
+        <v>-3.936593</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.111283</v>
+        <v>-3.11142</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.139298</v>
+        <v>-1.139738</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.162833</v>
+        <v>-1.163317</v>
       </c>
     </row>
     <row r="28">
@@ -2044,28 +2044,28 @@
         <v>-2.955304</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.86642</v>
+        <v>-2.868113</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.333994</v>
+        <v>-4.334704</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.13542</v>
+        <v>-5.140264</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.347599</v>
+        <v>-3.347702</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.936559</v>
+        <v>-3.936593</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.111283</v>
+        <v>-3.11142</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.139298</v>
+        <v>-1.139738</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.162833</v>
+        <v>-1.163317</v>
       </c>
     </row>
     <row r="30">
@@ -2295,25 +2295,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.055253</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.151145</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.777826</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.59106</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.022603</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.029674</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.07482</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.288627</v>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.055253</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.151145</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.777826</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.022109</v>
+        <v>0.613169</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.003401</v>
+        <v>0.026004</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.005102</v>
+        <v>0.034776</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.008503</v>
+        <v>0.08332299999999999</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.292028</v>
@@ -3065,25 +3065,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.062748</v>
+        <v>0.007495</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.165793</v>
+        <v>0.014648</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.7941049999999999</v>
+        <v>0.016279</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.606654</v>
+        <v>0.015594</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.040338</v>
+        <v>0.017735</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.037622</v>
+        <v>0.007948</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.08641500000000001</v>
+        <v>0.011595</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.117418</v>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">

--- a/output/pdf_financials_xlsx/URZ.xlsx
+++ b/output/pdf_financials_xlsx/URZ.xlsx
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.031829</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.001358</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0.025423</v>
@@ -2701,10 +2701,10 @@
         <v>0.016506</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.050637</v>
+        <v>0.082466</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.020869</v>
+        <v>0.022227</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.050846</v>
@@ -3086,10 +3086,10 @@
         <v>0.011595</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.117418</v>
+        <v>0.085589</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.027335</v>
+        <v>0.025977</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -3983,13 +3983,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.007766</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.025918</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -4142,52 +4142,52 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.051102</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.047934</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.043509</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.037474</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.038975</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.332008</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.033784</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.045573</v>
       </c>
     </row>
     <row r="68">
@@ -4307,31 +4307,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.025296</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.025063</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.007184</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.009381</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.01063</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.011381</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.012739</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.007013</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -4362,31 +4362,31 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0.025296</v>
+        <v>0.050592</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0.025063</v>
+        <v>0.050126</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.007184</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.009381</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.01063</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.011381</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.012739</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.007013</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
@@ -4588,25 +4588,25 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.007184</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.009381</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.04063</v>
+        <v>0.03</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.011381</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.012739</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.007013</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0</v>
@@ -4871,45 +4871,33 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.00965844886118551</v>
+        <v>0.01375894937966475</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.005561955078137242</v>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009925682738908996</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.001050915572157993</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>-0.2390368199770671</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>-0.03506480226156429</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.2814153602690272</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.01411884925670726</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.01113717319392148</v>
       </c>
       <c r="K80" s="1" t="inlineStr">
         <is>
@@ -6574,19 +6562,19 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013678</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.040299</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009756000000000001</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018671</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -7871,19 +7859,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013678</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.040299</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009756000000000001</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018671</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -7926,19 +7914,19 @@
         <v>-0.5053260000000001</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.543449</v>
+        <v>-0.557127</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.780393</v>
+        <v>-0.820692</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.53733</v>
+        <v>-0.547086</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.157693</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.077819</v>
+        <v>-1.09649</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-2.36965</v>
@@ -10206,7 +10194,11 @@
           <t>Current portion of finance lease obligations</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10302,7 +10294,11 @@
           <t>Current portion of finance lease obligations (Note 11)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.025296</v>
       </c>
@@ -11462,7 +11458,11 @@
           <t>Current portion of finance lease obligations (Note 12)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -15906,7 +15906,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -21100,7 +21104,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -21758,7 +21766,11 @@
           <t>Proceeds from private placement (Note 13)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
